--- a/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
+++ b/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
@@ -859,14 +859,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45182.62504732783</v>
+        <v>45217</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="23">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -921,16 +917,6 @@
       <c r="C12" s="36" t="n"/>
       <c r="D12" s="36" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23">
       <c r="C23" s="11" t="n"/>
     </row>
@@ -985,10 +971,8 @@
         </is>
       </c>
       <c r="C29" s="31" t="n"/>
-      <c r="D29" s="15" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
+      <c r="D29" s="15" t="n">
+        <v>112.86</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="23">
@@ -1023,9 +1007,6 @@
         <v>144.78</v>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="23">
       <c r="A35" s="25" t="n"/>
       <c r="B35" s="25" t="n"/>
@@ -1038,33 +1019,28 @@
     </row>
     <row r="37" ht="16.5" customHeight="1" s="23"/>
     <row r="38" ht="16.5" customHeight="1" s="23"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="23">
       <c r="A42" s="5" t="n"/>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="3" t="n"/>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B31:C31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
+++ b/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
@@ -972,7 +972,7 @@
       </c>
       <c r="C29" s="31" t="n"/>
       <c r="D29" s="15" t="n">
-        <v>112.86</v>
+        <v>118.503</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="23">
@@ -988,7 +988,7 @@
       </c>
       <c r="C30" s="34" t="n"/>
       <c r="D30" s="15" t="n">
-        <v>127.68</v>
+        <v>134.064</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="23">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="C31" s="31" t="n"/>
       <c r="D31" s="15" t="n">
-        <v>144.78</v>
+        <v>152.019</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" s="23">

--- a/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
+++ b/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
@@ -859,7 +859,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45217</v>
+        <v>45223</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="C29" s="31" t="n"/>
       <c r="D29" s="15" t="n">
-        <v>118.503</v>
+        <v>112.86</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="23">
@@ -988,7 +988,7 @@
       </c>
       <c r="C30" s="34" t="n"/>
       <c r="D30" s="15" t="n">
-        <v>134.064</v>
+        <v>127.68</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="23">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="C31" s="31" t="n"/>
       <c r="D31" s="15" t="n">
-        <v>152.019</v>
+        <v>144.78</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" s="23">
@@ -1030,17 +1030,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
+++ b/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
@@ -859,7 +859,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45223</v>
+        <v>45231</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>
@@ -1030,17 +1030,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
+++ b/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
@@ -859,7 +859,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45231</v>
+        <v>45232</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>

--- a/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
+++ b/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
@@ -859,7 +859,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45232</v>
+        <v>45234</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>

--- a/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
+++ b/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
@@ -859,7 +859,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45234</v>
+        <v>45237</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>

--- a/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
+++ b/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
@@ -988,7 +988,7 @@
       </c>
       <c r="C30" s="34" t="n"/>
       <c r="D30" s="15" t="n">
-        <v>127.68</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="23">
@@ -1030,17 +1030,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
+++ b/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
@@ -859,7 +859,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45237</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>
@@ -1030,17 +1030,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
+++ b/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
@@ -1030,17 +1030,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
+++ b/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
@@ -859,7 +859,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>
@@ -1030,17 +1030,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
+++ b/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
@@ -859,7 +859,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45254</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>

--- a/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
+++ b/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
@@ -859,7 +859,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>

--- a/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
+++ b/LISTAS/ma/TAPA UNIVERSAL Y CHUPETE DISMAY.xlsx
@@ -859,10 +859,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45266</v>
+        <v>45226.65158267139</v>
       </c>
       <c r="E1" s="2" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="23">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -917,6 +921,16 @@
       <c r="C12" s="36" t="n"/>
       <c r="D12" s="36" t="n"/>
     </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
     <row r="23">
       <c r="C23" s="11" t="n"/>
     </row>
@@ -971,8 +985,10 @@
         </is>
       </c>
       <c r="C29" s="31" t="n"/>
-      <c r="D29" s="15" t="n">
-        <v>112.86</v>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="23">
@@ -988,7 +1004,7 @@
       </c>
       <c r="C30" s="34" t="n"/>
       <c r="D30" s="15" t="n">
-        <v>134</v>
+        <v>150.66</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="23">
@@ -1004,9 +1020,12 @@
       </c>
       <c r="C31" s="31" t="n"/>
       <c r="D31" s="15" t="n">
-        <v>144.78</v>
-      </c>
-    </row>
+        <v>170.84</v>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="23">
       <c r="A35" s="25" t="n"/>
       <c r="B35" s="25" t="n"/>
@@ -1019,28 +1038,33 @@
     </row>
     <row r="37" ht="16.5" customHeight="1" s="23"/>
     <row r="38" ht="16.5" customHeight="1" s="23"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="23">
       <c r="A42" s="5" t="n"/>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="3" t="n"/>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B29:C29"/>
     <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
